--- a/output/pdf_financials_xlsx/WEB.xlsx
+++ b/output/pdf_financials_xlsx/WEB.xlsx
@@ -1304,7 +1304,7 @@
         <v>-3.076007</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="17">
@@ -1588,7 +1588,7 @@
         <v>-3.076007</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="21">
@@ -1753,7 +1753,7 @@
         <v>-3.076007</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="24">
@@ -2019,7 +2019,7 @@
         <v>-3.076007</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="28">
@@ -2129,7 +2129,7 @@
         <v>-2.928768</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>56.372173</v>
+        <v>-54.971343</v>
       </c>
     </row>
     <row r="30">
@@ -2271,7 +2271,7 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6073,7 +6073,7 @@
         <v>-3.076007</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="100">
@@ -7079,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.624767</v>
+        <v>0.566113</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -19223,7 +19223,7 @@
         <v>-3.076007</v>
       </c>
       <c r="T117" s="5" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="118">
@@ -35782,7 +35782,11 @@
           <t>Exploration and evaluation expenditures ‐</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -40259,7 +40263,7 @@
         <v>-3.076007</v>
       </c>
       <c r="T338" s="5" t="n">
-        <v>55.671758</v>
+        <v>-55.671758</v>
       </c>
     </row>
     <row r="339">

--- a/output/pdf_financials_xlsx/WEB.xlsx
+++ b/output/pdf_financials_xlsx/WEB.xlsx
@@ -956,13 +956,13 @@
         <v>0.013574</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.006659</v>
+        <v>0.098912</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.257676</v>
+        <v>0.1127</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.011745</v>
+        <v>0.06778000000000001</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.255344</v>
@@ -1017,7 +1017,7 @@
         <v>-0.1127</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.011745</v>
+        <v>-0.06778000000000001</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.645458</v>
@@ -1048,31 +1048,31 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003239</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.020375</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006123</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001762</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000558</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000521</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000499</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000539</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.007035</v>
       </c>
     </row>
     <row r="13">
@@ -1983,31 +1983,31 @@
         <v>-0.77105</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.101659</v>
+        <v>-0.104898</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.334932</v>
+        <v>-2.355307</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.504153</v>
+        <v>-1.510276</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-10.486903</v>
+        <v>-10.488665</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.228192</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.101745</v>
+        <v>-0.102303</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.111044</v>
+        <v>-0.111565</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.370376</v>
+        <v>-0.370875</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.056035</v>
+        <v>-0.056574</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-3.670956</v>
@@ -2019,7 +2019,7 @@
         <v>-3.076007</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-55.671758</v>
+        <v>-56.678793</v>
       </c>
     </row>
     <row r="28">
@@ -2093,31 +2093,31 @@
         <v>-0.77105</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.101659</v>
+        <v>-0.104898</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.334932</v>
+        <v>-2.355307</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.504153</v>
+        <v>-1.510276</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-10.486903</v>
+        <v>-10.488665</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.228192</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.101745</v>
+        <v>-0.102303</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.111044</v>
+        <v>-0.111565</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.370376</v>
+        <v>-0.370875</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.056035</v>
+        <v>-0.056574</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-3.662349</v>
@@ -2129,7 +2129,7 @@
         <v>-2.928768</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-54.971343</v>
+        <v>-55.978378</v>
       </c>
     </row>
     <row r="30">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.095648</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.111459</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.464604</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.371714</v>
@@ -2396,25 +2396,25 @@
         <v>0.098853</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004512</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.042412</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.011955</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.009717</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.008519000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.244436</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.645324</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2.822999</v>
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.095648</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.111459</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.464604</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.371714</v>
@@ -2506,25 +2506,25 @@
         <v>0.098853</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004512</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.042412</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.011955</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.009717</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.008519000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.244436</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.645324</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>2.822999</v>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.095648</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.111459</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.464684</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3166,25 +3166,25 @@
         <v>0.009313999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.009781</v>
+        <v>0.005269</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.045305</v>
+        <v>0.002893</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.011955</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.009717</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.012969</v>
+        <v>0.00445</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.290832</v>
+        <v>0.046396</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.819631</v>
+        <v>0.174307</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>30.037098</v>
@@ -7443,16 +7443,16 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.01065</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.084608</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.225085</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.740612</v>
       </c>
     </row>
     <row r="125">
@@ -7498,16 +7498,16 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.01065</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.084608</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.225085</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.740612</v>
       </c>
     </row>
     <row r="126">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -20938,7 +20938,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -39514,7 +39518,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -39614,7 +39618,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -41910,7 +41914,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -42634,17 +42638,17 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E364" s="5" t="n">
-        <v>-0.586632</v>
+        <v>0.586632</v>
       </c>
       <c r="F364" s="5" t="n">
-        <v>-0.311923</v>
+        <v>0.311923</v>
       </c>
       <c r="G364" s="5" t="n">
-        <v>-0.182654</v>
+        <v>0.182654</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
@@ -42657,25 +42661,25 @@
         </is>
       </c>
       <c r="J364" s="5" t="n">
-        <v>-1.611503</v>
+        <v>1.611503</v>
       </c>
       <c r="K364" s="5" t="n">
-        <v>-1.148781</v>
+        <v>1.148781</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>-0.250334</v>
+        <v>0.250334</v>
       </c>
       <c r="M364" s="5" t="n">
-        <v>-0.105174</v>
+        <v>0.105174</v>
       </c>
       <c r="N364" s="5" t="n">
-        <v>-0.098912</v>
+        <v>0.098912</v>
       </c>
       <c r="O364" s="5" t="n">
-        <v>-0.1127</v>
+        <v>0.1127</v>
       </c>
       <c r="P364" s="5" t="n">
-        <v>-0.06778000000000001</v>
+        <v>0.06778000000000001</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -42808,7 +42812,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -43658,7 +43662,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -46904,7 +46908,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -46928,10 +46932,10 @@
         </is>
       </c>
       <c r="I410" s="5" t="n">
-        <v>-2.392466</v>
+        <v>2.392466</v>
       </c>
       <c r="J410" s="5" t="n">
-        <v>-1.611503</v>
+        <v>1.611503</v>
       </c>
       <c r="K410" t="inlineStr">
         <is>
@@ -47590,7 +47594,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -47609,10 +47613,10 @@
         </is>
       </c>
       <c r="H417" s="5" t="n">
-        <v>-0.150622</v>
+        <v>0.150622</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>-2.392466</v>
+        <v>2.392466</v>
       </c>
       <c r="J417" t="inlineStr">
         <is>
@@ -47884,7 +47888,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -50776,7 +50780,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E450" s="5" t="n">

--- a/output/pdf_financials_xlsx/WEB.xlsx
+++ b/output/pdf_financials_xlsx/WEB.xlsx
@@ -38772,7 +38772,11 @@
           <t>Depreciation of right of use assets 11 $</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -38839,13 +38843,13 @@
         </is>
       </c>
       <c r="R323" s="5" t="n">
-        <v>-0.0469</v>
+        <v>0.0469</v>
       </c>
       <c r="S323" s="5" t="n">
-        <v>-0.147239</v>
+        <v>0.147239</v>
       </c>
       <c r="T323" s="5" t="n">
-        <v>-0.700415</v>
+        <v>0.700415</v>
       </c>
     </row>
     <row r="324">
@@ -41628,7 +41632,11 @@
           <t>Depreciation of right of use assets 10 $</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -41690,10 +41698,10 @@
         </is>
       </c>
       <c r="Q353" s="5" t="n">
-        <v>-0.008607</v>
+        <v>0.008607</v>
       </c>
       <c r="R353" s="5" t="n">
-        <v>-0.0469</v>
+        <v>0.0469</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WEB.xlsx
+++ b/output/pdf_financials_xlsx/WEB.xlsx
@@ -4266,16 +4266,16 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.196836</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.115445</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.326265</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>3.167772</v>
       </c>
     </row>
     <row r="68">
@@ -6504,16 +6504,16 @@
         <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.470258</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.963176</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>1.711454</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.620096</v>
       </c>
     </row>
     <row r="108">
@@ -6639,22 +6639,22 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.000428</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.001139</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.001017</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.001164</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.006544</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -19338,7 +19338,11 @@
           <t>Share based payment expense</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -28200,7 +28204,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -34810,7 +34818,11 @@
           <t>Accretion expense 1,139</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
